--- a/web/data/cleaned_file.xlsx
+++ b/web/data/cleaned_file.xlsx
@@ -425,31 +425,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>คำค้น</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัย</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>คณะ</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>หลักสูตร</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ประเภทหลักสูตร</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ค่าเทอม</t>
         </is>
@@ -458,1575 +463,1890 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>จุฬาลงกรณ์มหาวิทยาลัย</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมหุ่นยนต์</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมหุ่นยนต์และปัญญาประดิษฐ์ (หลักสูตรนานาชาติ)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>25500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยขอนแก่น ขอนแก่น</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมระบบวัดคุม วิศวกรรมอัตโนมัติ</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตรบัณฑิต (วิศวกรรมระบบอัตโนมัติ หุ่นยนต์ และปัญญาประดิษฐ์) วิศวกรรมระบบอัตโนมัติ หุ่นยนต์ และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเชียงใหม่ วิทยาเขตหลัก</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมหุ่นยนต์</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>วศ.บ.วิศวกรรมหุ่นยนต์และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>29000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยสงขลานครินทร์ หาดใหญ่</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>28000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยสงขลานครินทร์ ภูเก็ต</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>วิทยาลัยการคอมพิวเตอร์ &gt; วิศวกรรมปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>วศ.บ. วิศวกรรมปัญญาประดิษฐ์และระบบอัจฉริยะ</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>38000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>สถาบันเทคโนโลยีพระจอมเกล้าเจ้าคุณทหารลาดกระบัง ลาดกระบัง</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมหุ่นยนต์</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>วศ.บ. วิศวกรรมหุ่นยนต์และปัญญาประดิษฐ์ (หลักสูตรนานาชาติ)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>105000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>สถาบันเทคโนโลยีพระจอมเกล้าเจ้าคุณทหารลาดกระบัง ลาดกระบัง</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>วศ.บ. วิศวกรรมปัญญาประดิษฐ์และการเป็นผู้ประกอบการ (หลักสูตรนานาชาติ) (หลักสูตรร่วม สจล. และ ม.กรุงเทพ)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>175000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>สถาบันเทคโนโลยีพระจอมเกล้าเจ้าคุณทหารลาดกระบัง ลาดกระบัง</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>วิทยาลัยเทคโนโลยีและนวัตกรรมวัสดุ &gt; วิศวกรรมวัสดุ</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>วศ.บ. เทคโนโลยีวัสดุชาญฉลาด วศ.บ.วิศวกรรมหุ่นยนต์และปัญญาประดิษฐ์ (หลักสูตรนานาชาติ) หลักสูตรสองปริญญา</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>นานาชาติ พิเศษ</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>120000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยอุบลราชธานี วิทยาเขตหลัก</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>วศ.บ.สาขาวิชาวิศวกรรมปัญญาประดิษฐ์และการสั่งการ</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>28000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยวลัยลักษณ์</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตร์และเทคโนโลยี &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตรบัณฑิต สาขาวิศวกรรมคอมพิวเตอร์และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>32700</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีราชมงคลศรีวิชัย สงขลา</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมปัญญาประดิษฐ์และนวัตกรรมดิจิทัล</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>13750</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีราชมงคลอีสาน ขอนแก่น</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมเครื่องกล</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>วศ.บ.วิศวกรรมเครื่องกล-ระบบอัตโนมัติ หุ่นยนต์ และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยหอการค้าไทย</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต (วิศวกรรมคอมพิวเตอร์และปัญญาประดิษฐ์)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>42500</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีมหานคร</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>43571</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>วิศวกรรม ปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>สถาบันการจัดการปัญญาภิวัฒน์ แจ้งวัฒนะ นนทบุรี</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์และเทคโนโลยี &gt; วิศวกรรมปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>48000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>จุฬาลงกรณ์มหาวิทยาลัย</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>25500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>จุฬาลงกรณ์มหาวิทยาลัย</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์และเทคโนโลยีดิจิทัล</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>25500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเกษตรศาสตร์ บางเขน</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>24800</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเกษตรศาสตร์ กำแพงแสน</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์ กำแพงแสน &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>19500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเกษตรศาสตร์ ศรีราชา</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์ ศรีราชา &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์และสารสนเทศศาสตร์</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>29100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเกษตรศาสตร์ เฉลิมพระเกียรติ จ.สกลนคร</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>คณะวิทยาศาสตร์และวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยขอนแก่น ขอนแก่น</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>วิศวกรรมศาสตรบัณฑิต (วิศวกรรมคอมพิวเตอร์) วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเชียงใหม่ วิทยาเขตหลัก</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>23000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยธรรมศาสตร์ ศูนย์รังสิต</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>วศ.บ.สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>18900</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยธรรมศาสตร์ ศูนย์รังสิต</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>สถาบันเทคโนโลยีนานาชาติสิรินธร &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>วศ.บ.สาขาวิชาวิศวกรรมดิจิทัล และวิศวกรรมคอมพิวเตอร์ (หลักสูตรนานาชาติ) (SIIT)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>101200</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยมหิดล ศาลายา</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยศิลปากร สนามจันทร์</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมอิเล็กทรอนิกส์</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมอิเล็กทรอนิกส์และระบบคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>19000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยศิลปากร สนามจันทร์</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมอิเล็กทรอนิกส์</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมอิเล็กทรอนิกส์และระบบคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>ภาษาไทย พิเศษ</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>35000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยศรีนครินทรวิโรฒ องครักษ์</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยสงขลานครินทร์ หาดใหญ่</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีพระจอมเกล้าธนบุรี บางมด</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>วิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์ ปริญญาตรี 4 ปี (หลักสูตรนานาชาติ)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>70000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีพระจอมเกล้าธนบุรี บางมด</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>วิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์ ปริญญาตรี 4 ปี</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีพระจอมเกล้าพระนครเหนือ กรุงเทพฯ</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>สถาบันเทคโนโลยีพระจอมเกล้าเจ้าคุณทหารลาดกระบัง ลาดกระบัง</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>สถาบันเทคโนโลยีพระจอมเกล้าเจ้าคุณทหารลาดกระบัง ลาดกระบัง</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์ (หลักสูตรนานาชาติ)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>90000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>สถาบันเทคโนโลยีพระจอมเกล้าเจ้าคุณทหารลาดกระบัง ลาดกระบัง</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์และความปลอดภัยไซเบอร์</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>สถาบันเทคโนโลยีพระจอมเกล้าเจ้าคุณทหารลาดกระบัง ชุมพรเขตรอุดมศักดิ์ จังหวัดชุมพร</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>วิทยาเขตชุมพรเขตรอุดมศักดิ์ จังหวัดชุมพร &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีสุรนารี วิทยาเขตหลัก</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>สำนักวิชาวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>24637</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยนเรศวร วิทยาเขตหลัก</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>16000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยแม่ฟ้าหลวง</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>เทคโนโลยดิจิทัลประยุกต์ &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์ (จัดการเรียนการสอนเป็นภาษาอังกฤษ)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>28000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยนราธิวาสราชนครินทร์</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยพะเยา</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>คณะเทคโนโลยีสารสนเทศและการสื่อสาร &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
         <v>21000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยกาฬสินธุ์ วิทยาเขตหลัก</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
         <v>10150</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยรามคำแหง</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์ (วศ.บ. (วิศวกรรมคอมพิวเตอร์))</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
         <v>26000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยรามคำแหง</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสคร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์ (หลักสูตรนานาชาติ) (วศ.บ. (วิศวกรรมคอมพิวเตอร์))</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>50407</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>สถาบันเทคโนโลยีจิตรลดา</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>คณะเทคโนโลยีดิจิทัล &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>วิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
         <v>31500</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยราชภัฏพระนคร</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>คณะเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมอิเล็กทรอนิกส์</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>วศ.บ. 4 ปี วิศวกรรมอิเล็กทรอนิกส์อัจฉริยะและคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยราชภัฏพิบูลสงคราม</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>คณะเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยราชภัฏสวนสุนันทา</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
         <v>18500</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยราชภัฏอุบลราชธานี วิทยาเขตหลัก</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>คณะเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์และเครือข่าย</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
         <v>9076</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีราชมงคลธัญบุรี</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>คณะครุศาสตร์อุตสาหกรรม &gt; คอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีราชมงคลธัญบุรี</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีราชมงคลกรุงเทพ</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>วศ.บ. (วิศวกรรมคอมพิวเตอร์และระบบไอโอที)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
         <v>11700</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีราชมงคลพระนคร พระนครเหนือ</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีราชมงคลรัตนโกสินทร์ ศาลายา</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์ 4 ปี</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีราชมงคลศรีวิชัย สงขลา</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
         <v>13750</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีราชมงคลศรีวิชัย ตรัง</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์และเทคโนโลยี &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์และการสื่อสาร</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
         <v>13750</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเทคโนโลยีราชมงคลอีสาน นครราชสีมา</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>คณะวิศวกรรมศาสตร์และเทคโนโลยี &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
         <v>19000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยศรีปทุม</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>คณะเทคโนโลยีสารสนเทศ (กทม.) &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
         <v>46700</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยรังสิต</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>วิทยาลัยวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
         <v>49600</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยธุรกิจบัณฑิตย์</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>วิทยาลัยวิศวกรรมศาสตร์และเทคโนโลยี &gt; วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
         <v>42125</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยเกษมบัณฑิต วิทยาเขตร่มเกล้า</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
         <v>35250</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>วิศวกรรม คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>มหาวิทยาลัยสยาม วิทยาเขตหลัก</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
-        </is>
-      </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
         <v>37937</v>
       </c>
     </row>

--- a/web/data/cleaned_file.xlsx
+++ b/web/data/cleaned_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>สาขา</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>หลักสูตร</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ประเภทหลักสูตร</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ค่าเทอม</t>
         </is>
@@ -473,20 +478,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมหุ่นยนต์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>วิศวกรรมหุ่นยนต์</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมหุ่นยนต์และปัญญาประดิษฐ์ (หลักสูตรนานาชาติ)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>25500</v>
       </c>
     </row>
@@ -503,20 +513,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมระบบวัดคุม วิศวกรรมอัตโนมัติ</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>วิศวกรรมระบบวัดคุม วิศวกรรมอัตโนมัติ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>วิศวกรรมศาสตรบัณฑิต (วิศวกรรมระบบอัตโนมัติ หุ่นยนต์ และปัญญาประดิษฐ์) วิศวกรรมระบบอัตโนมัติ หุ่นยนต์ และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -533,20 +548,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมหุ่นยนต์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>วิศวกรรมหุ่นยนต์</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมหุ่นยนต์และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>29000</v>
       </c>
     </row>
@@ -563,20 +583,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>28000</v>
       </c>
     </row>
@@ -593,20 +618,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>วิทยาลัยการคอมพิวเตอร์ &gt; วิศวกรรมปัญญาประดิษฐ์</t>
+          <t>วิทยาลัยการคอมพิวเตอร์</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>วิศวกรรมปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมปัญญาประดิษฐ์และระบบอัจฉริยะ</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>38000</v>
       </c>
     </row>
@@ -623,20 +653,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมหุ่นยนต์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>วิศวกรรมหุ่นยนต์</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมหุ่นยนต์และปัญญาประดิษฐ์ (หลักสูตรนานาชาติ)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>105000</v>
       </c>
     </row>
@@ -653,20 +688,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมปัญญาประดิษฐ์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>วิศวกรรมปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมปัญญาประดิษฐ์และการเป็นผู้ประกอบการ (หลักสูตรนานาชาติ) (หลักสูตรร่วม สจล. และ ม.กรุงเทพ)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>175000</v>
       </c>
     </row>
@@ -683,20 +723,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>วิทยาลัยเทคโนโลยีและนวัตกรรมวัสดุ &gt; วิศวกรรมวัสดุ</t>
+          <t>วิทยาลัยเทคโนโลยีและนวัตกรรมวัสดุ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>วิศวกรรมวัสดุ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>วศ.บ. เทคโนโลยีวัสดุชาญฉลาด วศ.บ.วิศวกรรมหุ่นยนต์และปัญญาประดิษฐ์ (หลักสูตรนานาชาติ) หลักสูตรสองปริญญา</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>นานาชาติ พิเศษ</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>120000</v>
       </c>
     </row>
@@ -713,20 +758,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมปัญญาประดิษฐ์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>วิศวกรรมปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>วศ.บ.สาขาวิชาวิศวกรรมปัญญาประดิษฐ์และการสั่งการ</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>28000</v>
       </c>
     </row>
@@ -743,20 +793,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>วิศวกรรมศาสตร์และเทคโนโลยี &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>วิศวกรรมศาสตร์และเทคโนโลยี</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>วิศวกรรมศาสตรบัณฑิต สาขาวิศวกรรมคอมพิวเตอร์และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>32700</v>
       </c>
     </row>
@@ -773,20 +828,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมปัญญาประดิษฐ์และนวัตกรรมดิจิทัล</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>13750</v>
       </c>
     </row>
@@ -803,20 +863,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมเครื่องกล</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>วิศวกรรมเครื่องกล</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมเครื่องกล-ระบบอัตโนมัติ หุ่นยนต์ และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -833,20 +898,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต (วิศวกรรมคอมพิวเตอร์และปัญญาประดิษฐ์)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>42500</v>
       </c>
     </row>
@@ -863,20 +933,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>วิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>วิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>43571</v>
       </c>
     </row>
@@ -893,20 +968,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยี &gt; วิศวกรรมปัญญาประดิษฐ์</t>
+          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยี</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>วิศวกรรมปัญญาประดิษฐ์</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์และปัญญาประดิษฐ์</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>48000</v>
       </c>
     </row>
@@ -923,20 +1003,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>25500</v>
       </c>
     </row>
@@ -953,20 +1038,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์และเทคโนโลยีดิจิทัล</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>25500</v>
       </c>
     </row>
@@ -983,20 +1073,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>24800</v>
       </c>
     </row>
@@ -1013,20 +1108,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ กำแพงแสน &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์ กำแพงแสน</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -1043,20 +1143,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ ศรีราชา &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์ ศรีราชา</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์และสารสนเทศศาสตร์</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
         <v>29100</v>
       </c>
     </row>
@@ -1073,20 +1178,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>คณะวิทยาศาสตร์และวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิทยาศาสตร์และวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -1103,20 +1213,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>วิศวกรรมศาสตรบัณฑิต (วิศวกรรมคอมพิวเตอร์) วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -1133,20 +1248,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>23000</v>
       </c>
     </row>
@@ -1163,20 +1283,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>วศ.บ.สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
         <v>18900</v>
       </c>
     </row>
@@ -1193,20 +1318,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>สถาบันเทคโนโลยีนานาชาติสิรินธร &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>สถาบันเทคโนโลยีนานาชาติสิรินธร</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>วศ.บ.สาขาวิชาวิศวกรรมดิจิทัล และวิศวกรรมคอมพิวเตอร์ (หลักสูตรนานาชาติ) (SIIT)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>101200</v>
       </c>
     </row>
@@ -1223,20 +1353,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -1253,20 +1388,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมอิเล็กทรอนิกส์</t>
+          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>วิศวกรรมอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมอิเล็กทรอนิกส์และระบบคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>19000</v>
       </c>
     </row>
@@ -1283,20 +1423,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมอิเล็กทรอนิกส์</t>
+          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>วิศวกรรมอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมอิเล็กทรอนิกส์และระบบคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>ภาษาไทย พิเศษ</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>35000</v>
       </c>
     </row>
@@ -1313,20 +1458,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -1343,20 +1493,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
         <v>18000</v>
       </c>
     </row>
@@ -1373,20 +1528,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>วิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์ ปริญญาตรี 4 ปี (หลักสูตรนานาชาติ)</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>70000</v>
       </c>
     </row>
@@ -1403,20 +1563,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>วิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์ ปริญญาตรี 4 ปี</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -1433,20 +1598,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -1463,20 +1633,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -1493,20 +1668,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์ (หลักสูตรนานาชาติ)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>90000</v>
       </c>
     </row>
@@ -1523,20 +1703,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์และความปลอดภัยไซเบอร์</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -1553,20 +1738,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>วิทยาเขตชุมพรเขตรอุดมศักดิ์ จังหวัดชุมพร &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>วิทยาเขตชุมพรเขตรอุดมศักดิ์ จังหวัดชุมพร</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -1583,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>สำนักวิชาวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>สำนักวิชาวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1593,10 +1783,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
         <v>24637</v>
       </c>
     </row>
@@ -1613,20 +1808,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
         <v>16000</v>
       </c>
     </row>
@@ -1643,20 +1843,25 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>เทคโนโลยดิจิทัลประยุกต์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>เทคโนโลยดิจิทัลประยุกต์</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์ (จัดการเรียนการสอนเป็นภาษาอังกฤษ)</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
         <v>28000</v>
       </c>
     </row>
@@ -1673,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>วิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>วิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1683,10 +1888,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
         <v>14000</v>
       </c>
     </row>
@@ -1703,20 +1913,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>คณะเทคโนโลยีสารสนเทศและการสื่อสาร &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะเทคโนโลยีสารสนเทศและการสื่อสาร</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
         <v>21000</v>
       </c>
     </row>
@@ -1733,20 +1948,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
         <v>10150</v>
       </c>
     </row>
@@ -1763,20 +1983,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์ (วศ.บ. (วิศวกรรมคอมพิวเตอร์))</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
         <v>26000</v>
       </c>
     </row>
@@ -1793,20 +2018,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสคร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสคร์</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์ (หลักสูตรนานาชาติ) (วศ.บ. (วิศวกรรมคอมพิวเตอร์))</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>นานาชาติ</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>50407</v>
       </c>
     </row>
@@ -1823,20 +2053,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>คณะเทคโนโลยีดิจิทัล &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะเทคโนโลยีดิจิทัล</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>วิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
         <v>31500</v>
       </c>
     </row>
@@ -1853,20 +2088,25 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>คณะเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมอิเล็กทรอนิกส์</t>
+          <t>คณะเทคโนโลยีอุตสาหกรรม</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>วิศวกรรมอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>วศ.บ. 4 ปี วิศวกรรมอิเล็กทรอนิกส์อัจฉริยะและคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -1883,20 +2123,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>คณะเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะเทคโนโลยีอุตสาหกรรม</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -1913,20 +2158,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยีอุตสาหกรรม</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
         <v>18500</v>
       </c>
     </row>
@@ -1943,20 +2193,25 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>คณะเทคโนโลยีอุตสาหกรรม &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะเทคโนโลยีอุตสาหกรรม</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์และเครือข่าย</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
         <v>9076</v>
       </c>
     </row>
@@ -1973,20 +2228,25 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>คณะครุศาสตร์อุตสาหกรรม &gt; คอมพิวเตอร์</t>
+          <t>คณะครุศาสตร์อุตสาหกรรม</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>วิศวกรรมคอมพิวเตอร์</t>
+          <t>คอมพิวเตอร์</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
         <v>14000</v>
       </c>
     </row>
@@ -2003,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2013,10 +2273,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -2033,20 +2298,25 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>วศ.บ. (วิศวกรรมคอมพิวเตอร์และระบบไอโอที)</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
         <v>11700</v>
       </c>
     </row>
@@ -2063,20 +2333,25 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -2093,20 +2368,25 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์ 4 ปี</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -2123,20 +2403,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
         <v>13750</v>
       </c>
     </row>
@@ -2153,20 +2438,25 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยี &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยี</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>วศ.บ. วิศวกรรมคอมพิวเตอร์และการสื่อสาร</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
         <v>13750</v>
       </c>
     </row>
@@ -2183,20 +2473,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยี &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์และเทคโนโลยี</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
         <v>19000</v>
       </c>
     </row>
@@ -2213,20 +2508,25 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>คณะเทคโนโลยีสารสนเทศ (กทม.) &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะเทคโนโลยีสารสนเทศ (กทม.)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
         <v>46700</v>
       </c>
     </row>
@@ -2243,20 +2543,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>วิทยาลัยวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>วิทยาลัยวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
         <v>49600</v>
       </c>
     </row>
@@ -2273,20 +2578,25 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>วิทยาลัยวิศวกรรมศาสตร์และเทคโนโลยี &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>วิทยาลัยวิศวกรรมศาสตร์และเทคโนโลยี</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>หลักสูตรวิศวกรรมศาสตรบัณฑิต สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
         <v>42125</v>
       </c>
     </row>
@@ -2303,20 +2613,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>วศ.บ.วิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
         <v>35250</v>
       </c>
     </row>
@@ -2333,20 +2648,25 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>คณะวิศวกรรมศาสตร์ &gt; วิศวกรรมคอมพิวเตอร์</t>
+          <t>คณะวิศวกรรมศาสตร์</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>วิศวกรรมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>วศ.บ. สาขาวิชาวิศวกรรมคอมพิวเตอร์</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ภาษาไทย ปกติ</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ภาษาไทย ปกติ</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
         <v>37937</v>
       </c>
     </row>
